--- a/backend/uploads/temp/entregable_2.xlsx
+++ b/backend/uploads/temp/entregable_2.xlsx
@@ -1814,11 +1814,7 @@
           <t>Crear Cliente Jurídico Exitosamente</t>
         </is>
       </c>
-      <c r="D23" s="100" t="inlineStr">
-        <is>
-          <t>Tipo de cliente: Jurídico, Razón Social: LogistiCom S.A.S., Número de identificación: 987654321, Correo electrónico: info@logisticom.com, Número de contacto: 3209876543, Dirección: Avenida 456</t>
-        </is>
-      </c>
+      <c r="D23" s="100" t="inlineStr"/>
       <c r="E23" s="100" t="inlineStr">
         <is>
           <t>CA-01</t>
